--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487745_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487745_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. GASE SECO</t>
+          <t>G. MEJÍA ACOSTA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.6806</v>
+        <v>8.584199999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>6.9469</v>
+        <v>10.0858</v>
       </c>
       <c r="F2" t="n">
-        <v>2.7337</v>
+        <v>-1.5016</v>
       </c>
       <c r="G2" t="n">
-        <v>3.838</v>
+        <v>7.7478</v>
       </c>
       <c r="H2" t="n">
-        <v>3.2757</v>
+        <v>3.5369</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5623</v>
+        <v>4.2109</v>
       </c>
       <c r="J2" t="n">
-        <v>4.0629</v>
+        <v>9.5245</v>
       </c>
       <c r="K2" t="n">
-        <v>3.3449</v>
+        <v>4.3459</v>
       </c>
       <c r="L2" t="n">
-        <v>0.718</v>
+        <v>5.1786</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.225</v>
+        <v>-1.7767</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.0692</v>
+        <v>-0.8091</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.1557</v>
+        <v>-0.9677</v>
       </c>
       <c r="P2" t="n">
-        <v>2.7164</v>
+        <v>1.1642</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R2" t="n">
-        <v>2.7164</v>
+        <v>2.1344</v>
       </c>
       <c r="S2" t="n">
-        <v>2.8919</v>
+        <v>-0.3278</v>
       </c>
       <c r="T2" t="n">
-        <v>2.3676</v>
+        <v>0.3076</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5243</v>
+        <v>-0.6353</v>
       </c>
       <c r="V2" t="n">
-        <v>0.2343</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.5164</v>
+        <v>1.2239</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.2821</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>G. MEJÍA ACOSTA</t>
+          <t>O. BALSELLS PLAZA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>8.5786</v>
+        <v>7.8814</v>
       </c>
       <c r="E3" t="n">
-        <v>10.3255</v>
+        <v>5.4971</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.7469</v>
+        <v>2.3843</v>
       </c>
       <c r="G3" t="n">
-        <v>7.7478</v>
+        <v>4.9149</v>
       </c>
       <c r="H3" t="n">
-        <v>3.5369</v>
+        <v>2.8267</v>
       </c>
       <c r="I3" t="n">
-        <v>4.2109</v>
+        <v>2.0882</v>
       </c>
       <c r="J3" t="n">
-        <v>9.5245</v>
+        <v>5.1228</v>
       </c>
       <c r="K3" t="n">
-        <v>4.3459</v>
+        <v>3.1513</v>
       </c>
       <c r="L3" t="n">
-        <v>5.1786</v>
+        <v>1.9715</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.7767</v>
+        <v>-0.2079</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.8091</v>
+        <v>-0.3246</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.9677</v>
+        <v>0.1168</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1642</v>
+        <v>2.3284</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1344</v>
+        <v>2.3284</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3333</v>
+        <v>-0.0216</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5473</v>
+        <v>0.3743</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.8806</v>
+        <v>-0.3959</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.6597</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2239</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.2239</v>
+        <v>0.6597</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>O. BALSELLS PLAZA</t>
+          <t>A. GASE SECO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.7743</v>
+        <v>7.7129</v>
       </c>
       <c r="E4" t="n">
-        <v>4.3354</v>
+        <v>5.6061</v>
       </c>
       <c r="F4" t="n">
-        <v>2.4389</v>
+        <v>2.1068</v>
       </c>
       <c r="G4" t="n">
-        <v>4.9149</v>
+        <v>3.838</v>
       </c>
       <c r="H4" t="n">
-        <v>2.8267</v>
+        <v>3.2757</v>
       </c>
       <c r="I4" t="n">
-        <v>2.0882</v>
+        <v>0.5623</v>
       </c>
       <c r="J4" t="n">
-        <v>5.1228</v>
+        <v>4.0629</v>
       </c>
       <c r="K4" t="n">
-        <v>3.1513</v>
+        <v>3.3449</v>
       </c>
       <c r="L4" t="n">
-        <v>1.9715</v>
+        <v>0.718</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2079</v>
+        <v>-0.225</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3246</v>
+        <v>-0.0692</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1168</v>
+        <v>-0.1557</v>
       </c>
       <c r="P4" t="n">
-        <v>2.3284</v>
+        <v>2.7164</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3284</v>
+        <v>2.7164</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.1287</v>
+        <v>0.9242</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7874</v>
+        <v>1.0268</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3414</v>
+        <v>-0.1026</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6597</v>
+        <v>0.2343</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.5164</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6597</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.1688</v>
+        <v>5.1382</v>
       </c>
       <c r="E5" t="n">
-        <v>5.2812</v>
+        <v>5.1415</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1123</v>
+        <v>-0.0033</v>
       </c>
       <c r="G5" t="n">
         <v>3.8993</v>
@@ -844,13 +844,13 @@
         <v>1.3582</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9827</v>
+        <v>-1.0133</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.12</v>
+        <v>-0.2597</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.8627</v>
+        <v>-0.7537</v>
       </c>
       <c r="V5" t="n">
         <v>0.894</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4.0342</v>
+        <v>3.6244</v>
       </c>
       <c r="E6" t="n">
-        <v>4.3247</v>
+        <v>3.7241</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2905</v>
+        <v>-0.0997</v>
       </c>
       <c r="G6" t="n">
         <v>1.6353</v>
@@ -922,13 +922,13 @@
         <v>2.3284</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7586000000000001</v>
+        <v>0.3488</v>
       </c>
       <c r="T6" t="n">
-        <v>1.3358</v>
+        <v>0.7352</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5770999999999999</v>
+        <v>-0.3864</v>
       </c>
       <c r="V6" t="n">
         <v>0.2821</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2283</v>
+        <v>1.3339</v>
       </c>
       <c r="E7" t="n">
-        <v>0.963</v>
+        <v>0.8234</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2653</v>
+        <v>0.5105</v>
       </c>
       <c r="G7" t="n">
         <v>0.8082</v>
@@ -1000,13 +1000,13 @@
         <v>1.3582</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.3158</v>
+        <v>-1.2102</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1806</v>
+        <v>-0.3202</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.1352</v>
+        <v>-0.8899</v>
       </c>
       <c r="V7" t="n">
         <v>0.3776</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1889</v>
+        <v>1.1438</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2826</v>
+        <v>0.4828</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9063</v>
+        <v>0.661</v>
       </c>
       <c r="G8" t="n">
         <v>0.9379999999999999</v>
@@ -1078,13 +1078,13 @@
         <v>0.3881</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4192</v>
+        <v>-0.4643</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3634</v>
+        <v>-0.1632</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0558</v>
+        <v>-0.3011</v>
       </c>
       <c r="V8" t="n">
         <v>0.2821</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4411</v>
+        <v>0.7865</v>
       </c>
       <c r="E9" t="n">
-        <v>1.7117</v>
+        <v>1.8118</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2706</v>
+        <v>-1.0253</v>
       </c>
       <c r="G9" t="n">
         <v>0.6656</v>
@@ -1156,13 +1156,13 @@
         <v>1.1642</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.3887</v>
+        <v>-1.0433</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4845</v>
+        <v>-0.3844</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.9042</v>
+        <v>-0.6589</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.6599</v>
+        <v>-0.3323</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6661</v>
+        <v>-0.3658</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0062</v>
+        <v>0.0335</v>
       </c>
       <c r="G10" t="n">
         <v>-0.5446</v>
@@ -1234,13 +1234,13 @@
         <v>0.194</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3093</v>
+        <v>0.0182</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0606</v>
+        <v>0.2397</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2488</v>
+        <v>-0.2215</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.6261</v>
+        <v>-1.807</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.927</v>
+        <v>-2.0262</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3009</v>
+        <v>0.2192</v>
       </c>
       <c r="G11" t="n">
         <v>-1.437</v>
@@ -1312,13 +1312,13 @@
         <v>3.1045</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7712</v>
+        <v>0.048</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8479</v>
+        <v>0.053</v>
       </c>
       <c r="U11" t="n">
-        <v>0.07679999999999999</v>
+        <v>-0.005</v>
       </c>
       <c r="V11" t="n">
         <v>-0.6119</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.6438</v>
+        <v>-2.5982</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.768</v>
+        <v>-0.6679</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.8759</v>
+        <v>-1.9304</v>
       </c>
       <c r="G12" t="n">
         <v>1.261</v>
@@ -1390,13 +1390,13 @@
         <v>1.3582</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.1287</v>
+        <v>-1.0831</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6662</v>
+        <v>-0.5661</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4625</v>
+        <v>-0.517</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2239</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>31.165</v>
+        <v>31.4678</v>
       </c>
       <c r="E13" t="n">
-        <v>29.80990000000001</v>
+        <v>30.1127</v>
       </c>
       <c r="F13" t="n">
-        <v>1.3551</v>
+        <v>1.355</v>
       </c>
       <c r="G13" t="n">
         <v>23.7265</v>
@@ -1468,13 +1468,13 @@
         <v>18.433</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.1271</v>
+        <v>-3.824399999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>0.7400999999999999</v>
+        <v>1.043</v>
       </c>
       <c r="U13" t="n">
-        <v>-4.8672</v>
+        <v>-4.8673</v>
       </c>
       <c r="V13" t="n">
         <v>0.8940000000000001</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S. ABOUBACAR HIMA</t>
+          <t>J. FRANCES PASCUAL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.0679</v>
+        <v>1.0361</v>
       </c>
       <c r="E14" t="n">
-        <v>2.9455</v>
+        <v>2.7046</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.8776</v>
+        <v>-1.6685</v>
       </c>
       <c r="G14" t="n">
-        <v>0.109</v>
+        <v>0.0305</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5784</v>
+        <v>1.1839</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4694</v>
+        <v>-1.1534</v>
       </c>
       <c r="J14" t="n">
-        <v>1.35</v>
+        <v>2.318</v>
       </c>
       <c r="K14" t="n">
-        <v>1.2688</v>
+        <v>2.2368</v>
       </c>
       <c r="L14" t="n">
         <v>0.08119999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.241</v>
+        <v>-2.2875</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.6904</v>
+        <v>-1.0529</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.5506</v>
+        <v>-1.2346</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.9702</v>
+        <v>0.5821</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9702</v>
+        <v>-0.194</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>0.7761</v>
       </c>
       <c r="S14" t="n">
-        <v>2.3172</v>
+        <v>0.3098</v>
       </c>
       <c r="T14" t="n">
-        <v>1.9538</v>
+        <v>0.5807</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3634</v>
+        <v>-0.2708</v>
       </c>
       <c r="V14" t="n">
-        <v>0.6119</v>
+        <v>0.1137</v>
       </c>
       <c r="W14" t="n">
-        <v>0.6119</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>0.1137</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. FRANCES PASCUAL</t>
+          <t>S. ABOUBACAR HIMA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>0.9668</v>
       </c>
       <c r="E15" t="n">
-        <v>2.8047</v>
+        <v>1.8444</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.8048</v>
+        <v>-0.8776</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0305</v>
+        <v>0.109</v>
       </c>
       <c r="H15" t="n">
-        <v>1.1839</v>
+        <v>0.5784</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.1534</v>
+        <v>-0.4694</v>
       </c>
       <c r="J15" t="n">
-        <v>2.318</v>
+        <v>1.35</v>
       </c>
       <c r="K15" t="n">
-        <v>2.2368</v>
+        <v>1.2688</v>
       </c>
       <c r="L15" t="n">
         <v>0.08119999999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.2875</v>
+        <v>-1.241</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.0529</v>
+        <v>-0.6904</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.2346</v>
+        <v>-0.5506</v>
       </c>
       <c r="P15" t="n">
-        <v>0.5821</v>
+        <v>-0.9702</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.194</v>
+        <v>-0.9702</v>
       </c>
       <c r="R15" t="n">
-        <v>0.7761</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2736</v>
+        <v>1.2161</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6808</v>
+        <v>0.8527</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4071</v>
+        <v>0.3634</v>
       </c>
       <c r="V15" t="n">
-        <v>0.1137</v>
+        <v>0.6119</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.6119</v>
       </c>
       <c r="X15" t="n">
-        <v>0.1137</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.9234</v>
+        <v>-1.469</v>
       </c>
       <c r="E16" t="n">
-        <v>2.6732</v>
+        <v>2.3729</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.5966</v>
+        <v>-3.8419</v>
       </c>
       <c r="G16" t="n">
         <v>-2.881</v>
@@ -1702,13 +1702,13 @@
         <v>0.7761</v>
       </c>
       <c r="S16" t="n">
-        <v>0.9278</v>
+        <v>0.3822</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6202</v>
+        <v>0.3199</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3076</v>
+        <v>0.0623</v>
       </c>
       <c r="V16" t="n">
         <v>1.2239</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B. GUEYE</t>
+          <t>C. UNANUE CEGARRA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.1092</v>
+        <v>-2.7807</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1973</v>
+        <v>0.1617</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.3064</v>
+        <v>-2.9424</v>
       </c>
       <c r="G17" t="n">
-        <v>-4.1043</v>
+        <v>-2.9876</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.2607</v>
+        <v>-2.1396</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.8436</v>
+        <v>-0.848</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.0853</v>
+        <v>-0.3985</v>
       </c>
       <c r="K17" t="n">
-        <v>0.379</v>
+        <v>-0.2513</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.4643</v>
+        <v>-0.1473</v>
       </c>
       <c r="M17" t="n">
-        <v>-4.0189</v>
+        <v>-2.5891</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.6397</v>
+        <v>-1.8883</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.3792</v>
+        <v>-0.7008</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.9403</v>
+        <v>-0.3881</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.1045</v>
+        <v>-0.9702</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1642</v>
+        <v>0.5821</v>
       </c>
       <c r="S17" t="n">
-        <v>2.6933</v>
+        <v>0.595</v>
       </c>
       <c r="T17" t="n">
-        <v>2.2588</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4345</v>
+        <v>-0.3712</v>
       </c>
       <c r="V17" t="n">
-        <v>1.2421</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1283</v>
+        <v>0.5642</v>
       </c>
       <c r="X17" t="n">
-        <v>0.1137</v>
+        <v>-0.5642</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. UNANUE CEGARRA</t>
+          <t>C. KLOTZ MAROTO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.9621</v>
+        <v>-2.8184</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3619</v>
+        <v>-0.3209</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.3239</v>
+        <v>-2.4975</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.9876</v>
+        <v>-3.9857</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.1396</v>
+        <v>-2.3101</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.848</v>
+        <v>-1.6756</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.3985</v>
+        <v>-0.5468</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.2513</v>
+        <v>-0.6508</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.1473</v>
+        <v>0.104</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.5891</v>
+        <v>-3.4389</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.8883</v>
+        <v>-1.6593</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.7008</v>
+        <v>-1.7796</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.3881</v>
+        <v>0.3881</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9702</v>
+        <v>-0.194</v>
       </c>
       <c r="R18" t="n">
         <v>0.5821</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4136</v>
+        <v>0.7133</v>
       </c>
       <c r="T18" t="n">
-        <v>1.1664</v>
+        <v>0.42</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7528</v>
+        <v>0.2933</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.066</v>
       </c>
       <c r="W18" t="n">
-        <v>0.5642</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.5642</v>
+        <v>0.066</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. KLOTZ MAROTO</t>
+          <t>B. GUEYE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.1192</v>
+        <v>-3.4283</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.3218</v>
+        <v>-0.9038</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.7973</v>
+        <v>-2.5245</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.9857</v>
+        <v>-4.1043</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.3101</v>
+        <v>-2.2607</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.6756</v>
+        <v>-1.8436</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.5468</v>
+        <v>-0.0853</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6508</v>
+        <v>0.379</v>
       </c>
       <c r="L19" t="n">
-        <v>0.104</v>
+        <v>-0.4643</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.4389</v>
+        <v>-4.0189</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.6593</v>
+        <v>-2.6397</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.7796</v>
+        <v>-1.3792</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3881</v>
+        <v>-1.9403</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.194</v>
+        <v>-3.1045</v>
       </c>
       <c r="R19" t="n">
-        <v>0.5821</v>
+        <v>1.1642</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5875</v>
+        <v>1.3742</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.581</v>
+        <v>1.1577</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0065</v>
+        <v>0.2165</v>
       </c>
       <c r="V19" t="n">
-        <v>0.066</v>
+        <v>1.2421</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.1283</v>
       </c>
       <c r="X19" t="n">
-        <v>0.066</v>
+        <v>0.1137</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.5645</v>
+        <v>-4.1185</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8813</v>
+        <v>-0.3808</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.6832</v>
+        <v>-3.7378</v>
       </c>
       <c r="G20" t="n">
         <v>-1.331</v>
@@ -2014,13 +2014,13 @@
         <v>0.9702</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.2129</v>
+        <v>-0.7669</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7145</v>
+        <v>-0.214</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4984</v>
+        <v>-0.5528999999999999</v>
       </c>
       <c r="V20" t="n">
         <v>0.1137</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.6058</v>
+        <v>-4.6786</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0802</v>
+        <v>-2.1802</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.5256</v>
+        <v>-2.4984</v>
       </c>
       <c r="G21" t="n">
         <v>-3.344</v>
@@ -2092,13 +2092,13 @@
         <v>0.7761</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0305</v>
+        <v>-0.0423</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2434</v>
+        <v>0.1433</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2129</v>
+        <v>-0.1856</v>
       </c>
       <c r="V21" t="n">
         <v>0.066</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.7396</v>
+        <v>-6.2301</v>
       </c>
       <c r="E22" t="n">
         <v>-1.6159</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.1237</v>
+        <v>-4.6143</v>
       </c>
       <c r="G22" t="n">
         <v>-2.9031</v>
@@ -2170,13 +2170,13 @@
         <v>1.1642</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3874</v>
+        <v>-0.1032</v>
       </c>
       <c r="T22" t="n">
         <v>0.1962</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1912</v>
+        <v>-0.2994</v>
       </c>
       <c r="V22" t="n">
         <v>-2.4477</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-9.209300000000001</v>
+        <v>-7.6443</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.4386</v>
+        <v>-3.0372</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.7707</v>
+        <v>-4.6072</v>
       </c>
       <c r="G23" t="n">
         <v>-2.3293</v>
@@ -2248,13 +2248,13 @@
         <v>0.9702</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1157</v>
+        <v>0.4492</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9567</v>
+        <v>0.4447</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.159</v>
+        <v>0.0045</v>
       </c>
       <c r="V23" t="n">
         <v>-1.8836</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-31.16520000000001</v>
+        <v>-31.165</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.355200000000001</v>
+        <v>-1.3552</v>
       </c>
       <c r="F24" t="n">
-        <v>-29.8098</v>
+        <v>-29.8101</v>
       </c>
       <c r="G24" t="n">
         <v>-23.7265</v>
@@ -2323,16 +2323,16 @@
         <v>-18.4331</v>
       </c>
       <c r="R24" t="n">
-        <v>7.7613</v>
+        <v>7.761299999999999</v>
       </c>
       <c r="S24" t="n">
-        <v>4.1273</v>
+        <v>4.1274</v>
       </c>
       <c r="T24" t="n">
-        <v>4.867400000000001</v>
+        <v>4.8674</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.7400000000000002</v>
+        <v>-0.7398999999999999</v>
       </c>
       <c r="V24" t="n">
         <v>-0.8940000000000001</v>
